--- a/20260804_従業員管理_02_検証プラン.xlsx
+++ b/20260804_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$3:$L$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$3:$L$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -527,14 +527,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>従業員管理 検証プラン ─ 操作した結果が受入条件を満たすか（準備11行＋検証54件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="42" customHeight="1">
+          <t>従業員管理 検証プラン ─ 操作した結果が受入条件を満たすか（準備11行＋検証59件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="46" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>上から順に実施します。S-01〜S-11が準備、T-／C-が検証、R-01〜R-05は画面操作では判別できない実装物のレビューです。S-02（算式の確定）とS-03（サンプルデータ再作成）はゲート。ケース単位の結果は「確認表」で条件単位に集約します。黄色が記入欄。スクリーンショットは ID.png で保存。</t>
+          <t>上から順に実施します。S-01〜S-11が準備、T-／C-が検証、R-01〜R-06は画面操作では判別できない実装物のレビューです。S-02（算式の確定）とS-03（サンプルデータ再作成）はゲート。ケース単位の結果は「01_確認表」で条件単位に集約します。黄色が記入欄。スクリーンショットは ID.png で保存。</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>data/07（KOT）・08（ジョブカン）・09（異常系）・10（給与設定）・11（先頭説明行あり）を手元に用意し、data/12（設定未入力のEMP-015）を投入</t>
+          <t>data/07（KOT）・08（ジョブカン）・09（異常系）・10（給与設定）・11（先頭説明行あり）を手元に用意し、data/12（設定未入力のEMP-015）を投入。あわせて data/16・17（前回取込の差分確認用）を用意</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>09は4行が別種のエラー（コード欠落／給与額-50,000／店舗S99／給与額abc・雇用区分「契約社員」）</t>
+          <t>09は4行が別種のエラー（コード欠落／給与額-50,000／店舗S99／給与額abc・雇用区分「契約社員」） ／ 16・17は T-N02（前回差分表示）で使用</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>T-A05</t>
+          <t>T-A09</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>AC-49</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>日別実績の表示</t>
+          <t>人件費実績からの設定編集</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
+          <t>人件費実績で対象従業員の「従業員設定」を開き、単位給与額を変更して「更新保存」→ 従業員詳細の設定変更履歴を確認</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
+          <t>モーダルに14項目が表示される。更新保存で人件費実績に戻り数字が再計算される。**従業員詳細の履歴が1行増え、変更ソースが記録される**（詳細から編集した場合と同じ形式）</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr"/>
@@ -2096,7 +2096,7 @@
       <c r="K33" s="8" t="inlineStr"/>
       <c r="L33" s="8" t="inlineStr">
         <is>
-          <t>概算の日割りは判断1が未確定のため出さない仕様</t>
+          <t>★入口が2つある（判断10）。モーダル経由だけ履歴が残らないと原則①が破れる。R-06で実装も確認</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>T-A07</t>
+          <t>T-A05</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>AC-36</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>実績のCSVエクスポート</t>
+          <t>日別実績の表示</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
+          <t>日別実績タブに切り替え、日付／店舗／雇用区分／検索で絞り込む</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>表示中のタブ・モード・フィルタの内容が出力される。日本語が文字化けしない</t>
+          <t>全21列（名前/給与単位/単位給与額/想定勤務時間/勤務時間/勤務時間実績差分/みなし残業時間/みなし残業時間差分/想定給与/給与/給与実績差分/所属店舗/所属店舗労働時間/ヘルプ先店舗/ヘルプ時間/ヘルプ人件費/深夜残業時間/深夜残業代/所属店舗交通費/ヘルプ交通費/総支給額）。交通費は所属店舗ぶんと応援先ぶんが別列。概算モードは存在しない</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr"/>
@@ -2146,19 +2146,19 @@
       <c r="K34" s="8" t="inlineStr"/>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t>全件出力になっていないこと</t>
+          <t>概算の日割りは判断1が未確定のため出さない仕様</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>締め</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>T-S01</t>
+          <t>T-A07</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -2168,27 +2168,27 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>AC-18</t>
+          <t>AC-36</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>締めボタンの表示条件</t>
+          <t>実績のCSVエクスポート</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>S-08</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
-          <t>月別実績タブと日別実績タブを順に開く</t>
+          <t>月別（実績モード）と日別でそれぞれCSVエクスポートし、Excelで開く</t>
         </is>
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>月別のみ「2026-05 締め」が表示。日別には表示されない</t>
+          <t>表示中のタブ・モード・フィルタの内容が出力される。日本語が文字化けしない</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr"/>
@@ -2196,19 +2196,19 @@
       <c r="K35" s="8" t="inlineStr"/>
       <c r="L35" s="8" t="inlineStr">
         <is>
-          <t>締めの単位が「月」であることの明示</t>
+          <t>全件出力になっていないこと</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>締め</t>
+          <t>実績</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>T-S03</t>
+          <t>T-A08</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -2218,27 +2218,27 @@
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>AC-16 AC-19 AC-32</t>
+          <t>AC-48</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>締めの実行</t>
+          <t>勤怠実績の取込</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>S-06 S-08</t>
+          <t>S-05 S-08</t>
         </is>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>年月＝2026-05を選び「締め」→ 確認モーダルの内容を確認 → 実行</t>
+          <t>人件費実績の右上「実績データ取込」を押す。取込中モーダルが出ている間に締めボタンなど他の操作を試す</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>「締め後はデータの編集ができなくなります」の確認モーダルが**1回**出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
+          <t>「実績データ取込中」のモーダルが出て進捗が表示される（0%→100%）。処理中は他の操作を受け付けない。完了後、実績モードの列に金額が入る（未反映=0件）</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr"/>
@@ -2246,7 +2246,7 @@
       <c r="K36" s="8" t="inlineStr"/>
       <c r="L36" s="8" t="inlineStr">
         <is>
-          <t>設定未入力のEMP-015がいる状態で事前警告が出るかを所見に記録（AC-32・次段階）</t>
+          <t>★この取込を行うまで実績の数字は出ない。締め（T-S03）はこの後に実施する</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>T-S04</t>
+          <t>T-S01</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -2268,27 +2268,27 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-18</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>締め後は編集できない</t>
+          <t>締めボタンの表示条件</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>T-S03実施済み</t>
+          <t>S-08</t>
         </is>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
-          <t>2026-05の実績を編集／勤怠を再取込しようとする</t>
+          <t>月別実績タブと日別実績タブを順に開く</t>
         </is>
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>編集できない（または反映されない）</t>
+          <t>月別のみ「2026-05 締め」が表示。日別には表示されない</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       <c r="K37" s="8" t="inlineStr"/>
       <c r="L37" s="8" t="inlineStr">
         <is>
-          <t>金額の不変は C-008 で数値検証</t>
+          <t>締めの単位が「月」であることの明示</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>T-D07</t>
+          <t>T-S03</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -2318,27 +2318,27 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>AC-20</t>
+          <t>AC-16 AC-19 AC-32</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>締め済み期間への遡及</t>
+          <t>締めの実行</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>T-S03実施済み S-07</t>
+          <t>S-06 S-08</t>
         </is>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>EMP-001に適用日付＝2026-05-10で保存を試行</t>
+          <t>年月＝2026-05を選び「締め」→ 確認モーダルの内容を確認 → 実行</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
+          <t>「締め後はデータの編集ができなくなります」の確認モーダルが**1回**出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -2346,7 +2346,7 @@
       <c r="K38" s="8" t="inlineStr"/>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t>既定は将来適用。モック未実装のため実装確認が必要</t>
+          <t>設定未入力のEMP-015がいる状態で事前警告が出るかを所見に記録（AC-32・次段階）</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>T-S05</t>
+          <t>T-S04</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>AC-17 AC-19</t>
+          <t>AC-16</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>締めの解除</t>
+          <t>締め後は編集できない</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>「締め解除」→ 確認モーダル → 実行</t>
+          <t>2026-05の実績を編集／勤怠を再取込しようとする</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>「解除後はデータの編集が可能になります」の確認が出る（1回）。実行で編集可に戻り、C-008で保留されていた5/10からの改定が反映される。EMP-001の2026-05の実績給与＝**352,286円**（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）。締め前の338,000から+14,286円</t>
+          <t>編集できない（または反映されない）</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
@@ -2396,7 +2396,7 @@
       <c r="K39" s="8" t="inlineStr"/>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>所定労働日割（判断1）で再計算される。暦日割で実装されていると概算333,548→実績351,548になり、この差738円で基準を判別できる</t>
+          <t>金額の不変は C-008 で数値検証</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>T-S07</t>
+          <t>T-D07</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -2418,27 +2418,27 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>AC-41</t>
+          <t>AC-20</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>締めの実行権限</t>
+          <t>締め済み期間への遡及</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>S-10 S-08</t>
+          <t>T-S03実施済み S-07</t>
         </is>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
+          <t>EMP-001に適用日付＝2026-05-10で保存を試行</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
+          <t>締め済み期間のため反映されない旨の警告が出る（黙って保存されない）</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr"/>
@@ -2446,19 +2446,19 @@
       <c r="K40" s="8" t="inlineStr"/>
       <c r="L40" s="8" t="inlineStr">
         <is>
-          <t>店長が自店だけ締められると月次が分断される。権限設定のリリース範囲に依存</t>
+          <t>既定は将来適用。モック未実装のため実装確認が必要</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>締め</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>T-I02</t>
+          <t>T-S05</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -2468,27 +2468,27 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>AC-21 AC-30</t>
+          <t>AC-17 AC-19</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>テンプレートのDLと画面</t>
+          <t>締めの解除</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>T-S03実施済み</t>
         </is>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
+          <t>「締め解除」→ 確認モーダル → 実行</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>従業員設定＝**6列**（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝**9列**（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
+          <t>「解除後はデータの編集が可能になります」の確認が出る（1回）。実行で編集可に戻り、C-008で保留されていた5/10からの改定が反映される。EMP-001の2026-05の実績給与＝**352,286円**（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）。締め前の338,000から+14,286円</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
@@ -2496,19 +2496,19 @@
       <c r="K41" s="8" t="inlineStr"/>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>列が登録フォーム（T-R02の13項目）と対応していること。BOM付きUTF-8</t>
+          <t>所定労働日割（判断1）で再計算される。暦日割で実装されていると概算333,548→実績351,548になり、この差738円で基準を判別できる</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>取込</t>
+          <t>締め</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>T-I03</t>
+          <t>T-S07</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -2518,27 +2518,27 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>AC-21</t>
+          <t>AC-41</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>King of Time形式の取込</t>
+          <t>締めの実行権限</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>S-04 S-06</t>
+          <t>S-10 S-08</t>
         </is>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>データ種類＝King of Time を選び data/07（従業員設定・3行）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
+          <t>店長スコープのアカウントでログインし、人件費実績を開いて締めを試みる</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
+          <t>締めボタンが表示されない、または実行できない（会社スコープのみ実行可）</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr"/>
@@ -2546,7 +2546,7 @@
       <c r="K42" s="8" t="inlineStr"/>
       <c r="L42" s="8" t="inlineStr">
         <is>
-          <t>既存は更新・新規は追加という挙動になること（重複追加でないこと）。従業員設定と給与設定が別テンプレートで運用できること</t>
+          <t>店長が自店だけ締められると月次が分断される。権限設定のリリース範囲に依存</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>T-I04</t>
+          <t>T-I02</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -2568,27 +2568,27 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>AC-22</t>
+          <t>AC-21 AC-30</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>ジョブカン形式（表記ゆれ）の取込</t>
+          <t>テンプレートのDLと画面</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>S-04 S-06</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>データ種類＝ジョブカン を選び data/08（3行）をD&amp;D → 登録</t>
+          <t>設定インポートを開き、「従業員設定CSVテンプレート」「給与設定CSVテンプレート」をDLしてExcelで開く</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
+          <t>従業員設定＝**6列**（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝**9列**（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
@@ -2596,7 +2596,7 @@
       <c r="K43" s="8" t="inlineStr"/>
       <c r="L43" s="8" t="inlineStr">
         <is>
-          <t>スタッフコード/スタッフ名/雇用形態 の表記ゆれが吸収されること</t>
+          <t>列が登録フォーム（T-R02の13項目）と対応していること。BOM付きUTF-8</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>T-I05</t>
+          <t>T-I03</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>AC-23</t>
+          <t>AC-21</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>異常系データの検出</t>
+          <t>King of Time形式の取込</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>data/09（4行）をD&amp;D → 登録</t>
+          <t>データ種類＝King of Time を選び data/07（従業員設定・3行）をD&amp;D → 登録。続けて data/10（給与設定・3行）を取り込む</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
+          <t>07は3行すべて取り込まれ、EMP-001=340,000・EMP-005=360,000に更新、EMP-013は新規追加。10は給与設定（ヘルプ先交通費 S02:700;S03:900 の記法を含む）が反映される</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr"/>
@@ -2646,7 +2646,7 @@
       <c r="K44" s="8" t="inlineStr"/>
       <c r="L44" s="8" t="inlineStr">
         <is>
-          <t>行単位エラーか全体拒否かを記録し、仕様として確定する</t>
+          <t>既存は更新・新規は追加という挙動になること（重複追加でないこと）。従業員設定と給与設定が別テンプレートで運用できること</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>T-I17</t>
+          <t>T-I04</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -2668,12 +2668,12 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>AC-40</t>
+          <t>AC-22</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>二重登録の防止</t>
+          <t>ジョブカン形式（表記ゆれ）の取込</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>（a）data/07を2回続けて取り込む （b）同じ従業員コードが2行あるCSVを作って取り込む</t>
+          <t>データ種類＝ジョブカン を選び data/08（3行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
+          <t>3行すべて取り込まれる（EMP-003=1,250・EMP-010=1,300・EMP-014は新規）</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
       <c r="K45" s="8" t="inlineStr"/>
       <c r="L45" s="8" t="inlineStr">
         <is>
-          <t>二重登録されると人件費が二重計上され、店舗別合計＝全社（AC-11）が壊れる</t>
+          <t>スタッフコード/スタッフ名/雇用形態 の表記ゆれが吸収されること</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>T-I18</t>
+          <t>T-I05</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>AC-42</t>
+          <t>AC-23</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>取込が途中で失敗したときの扱い</t>
+          <t>異常系データの検出</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
+          <t>data/09（4行）をD&amp;D → 登録</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>部分的に登録された行が残らない（全体拒否）か、正常行のみ登録され異常行が明示される（行単位）。**どちらであっても、中途半端な状態が残らない**</t>
+          <t>4行すべてがエラーとして検出され登録されない（見逃し0）。EMP-001の給与額が負値にならず、店舗S99が自動作成されない</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr"/>
@@ -2746,7 +2746,7 @@
       <c r="K46" s="8" t="inlineStr"/>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t>T-I05は「エラーが検出されること」、本ケースは「登録の結果が説明できる状態であること」を見る</t>
+          <t>行単位エラーか全体拒否かを記録し、仕様として確定する</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>T-I11</t>
+          <t>T-I17</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -2768,27 +2768,27 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>AC-37</t>
+          <t>AC-40</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>CSV位置合わせ設定</t>
+          <t>二重登録の防止</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>S-06</t>
+          <t>S-04 S-06</t>
         </is>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
+          <t>（a）data/07を2回続けて取り込む （b）同じ従業員コードが2行あるCSVを作って取り込む</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>余計な行が無視され、3行が正しく取り込まれる</t>
+          <t>（a）2回目は更新となり件数が増えない （b）重複行がエラーとして検出される（両方が登録されない）</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr"/>
@@ -2796,7 +2796,7 @@
       <c r="K47" s="8" t="inlineStr"/>
       <c r="L47" s="8" t="inlineStr">
         <is>
-          <t>勤怠システムの出力にありがちな先頭行ズレを吸収できること</t>
+          <t>二重登録されると人件費が二重計上され、店舗別合計＝全社（AC-11）が壊れる</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>T-I09</t>
+          <t>T-I18</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -2818,27 +2818,27 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>AC-24 AC-38 AC-30</t>
+          <t>AC-42</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>列マッピングテンプレート</t>
+          <t>取込が途中で失敗したときの扱い</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>S-06</t>
+          <t>S-04 S-06</t>
         </is>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
-          <t>「列マッピングテンプレート管理」→ 登録 → データ種類で絞り込み → 編集・削除 → 列マッピング表インポート → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択</t>
+          <t>data/09（4行中すべてが異常）を取り込み、取込後の従業員一覧と設定履歴を確認する</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>テンプレートが保存・絞り込み・編集・削除できる。マッピング表の一括登録ができる。往復導線が通る。選択すると取込列設定が自動で埋まる（手入力0項目）</t>
+          <t>部分的に登録された行が残らない（全体拒否）か、正常行のみ登録され異常行が明示される（行単位）。**どちらであっても、中途半端な状態が残らない**</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
@@ -2846,19 +2846,19 @@
       <c r="K48" s="8" t="inlineStr"/>
       <c r="L48" s="8" t="inlineStr">
         <is>
-          <t>CSだけで完結できること（開発不要）が要件</t>
+          <t>T-I05は「エラーが検出されること」、本ケースは「登録の結果が説明できる状態であること」を見る</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I11</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -2868,27 +2868,27 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-37</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>CSV位置合わせ設定</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-06</t>
         </is>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②対象＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>data/11（先頭に説明行2行）をD&amp;D → 位置合わせ設定でヘッダー行＝3／データ開始行＝4／開始列＝1を指定 → 登録</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>余計な行が無視され、3行が正しく取り込まれる</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr"/>
@@ -2896,19 +2896,19 @@
       <c r="K49" s="8" t="inlineStr"/>
       <c r="L49" s="8" t="inlineStr">
         <is>
-          <t>チェックしていない列が混入しないこと（情報の出し過ぎ防止）</t>
+          <t>勤怠システムの出力にありがちな先頭行ズレを吸収できること</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-I09</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -2918,27 +2918,27 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>AC-25</t>
+          <t>AC-24 AC-38 AC-30</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>列マッピングテンプレート</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-06</t>
         </is>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>「列マッピングテンプレート管理」→ 登録 → データ種類で絞り込み → 編集・削除 → 列マッピング表インポート → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
+          <t>テンプレートが保存・絞り込み・編集・削除できる。マッピング表の一括登録ができる。往復導線が通る。選択すると取込列設定が自動で埋まる（手入力0項目）</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
       <c r="K50" s="8" t="inlineStr"/>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>①の複数選択が出力まで反映されること</t>
+          <t>CSだけで完結できること（開発不要）が要件</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -2968,12 +2968,12 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>AC-27 AC-28</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>未選択の防止と文字化け</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -2983,12 +2983,12 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>種別／対象／項目のいずれかを未選択のまま「エクスポート」→ その後T-E04の出力ファイルをExcelで開く</t>
+          <t>従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②対象＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>警告が出て出力されない（空ファイルが落ちてこない）。日本語が文字化けしない（BOM付きUTF-8）</t>
+          <t>専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
@@ -2996,19 +2996,19 @@
       <c r="K51" s="8" t="inlineStr"/>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>そのまま外部提出できるかの判断</t>
+          <t>チェックしていない列が混入しないこと（情報の出し過ぎ防止）</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -3018,27 +3018,27 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-25</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>T-I03実施済み</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
+          <t>①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
+          <t>実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr"/>
@@ -3046,19 +3046,19 @@
       <c r="K52" s="8" t="inlineStr"/>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>履歴の「変更ソース＝CSVインポート」から辿れること</t>
+          <t>①の複数選択が出力まで反映されること</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -3068,27 +3068,27 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>AC-01 AC-02 AC-03</t>
+          <t>AC-27 AC-28</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合</t>
+          <t>未選択の防止と文字化け</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>S-09 S-11</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>移行を実施し、移行後の従業員一覧・設定履歴・直近3か月の人件費実績を出力して data/15 で突合</t>
+          <t>種別／対象／項目のいずれかを未選択のまま「エクスポート」→ その後T-E04の出力ファイルをExcelで開く</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>件数の増減＝0／全項目の差分＝0／適用日付が空の行＝0／3か月とも人件費の差分＝0円</t>
+          <t>警告が出て出力されない（空ファイルが落ちてこない）。日本語が文字化けしない（BOM付きUTF-8）</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
@@ -3096,19 +3096,19 @@
       <c r="K53" s="8" t="inlineStr"/>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>★No-Go条件。1件・1円でも動けばリリース中止</t>
+          <t>そのまま外部提出できるかの判断</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -3118,27 +3118,27 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>T-I03実施済み</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr"/>
@@ -3146,19 +3146,19 @@
       <c r="K54" s="8" t="inlineStr"/>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>欠落0であること</t>
+          <t>履歴の「変更ソース＝CSVインポート」から辿れること</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -3168,27 +3168,27 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>S-04 S-05</t>
+          <t>S-06 S-12</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回330,000円→新規350,000円」の形式で差だけが表示される。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr"/>
@@ -3196,49 +3196,49 @@
       <c r="K55" s="8" t="inlineStr"/>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>キャンセル・戻るを含む</t>
+          <t>タブ（設定＝従業員設定/給与設定、実績＝月別データ/日別データ）も切り替わること</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>取込データと人件費実績の相互導線</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>2026-05の EMP-002（概算280,000・深夜2h=2,800）と EMP-007（概算300,000・深夜4h=6,000）を検算</t>
+          <t>人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
+          <t>2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr"/>
@@ -3246,49 +3246,49 @@
       <c r="K56" s="8" t="inlineStr"/>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>現行サンプルはこの2行のみ一致している</t>
+          <t>行きと戻りの両方が通ること</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>横断</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-01 AC-02 AC-03</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>移行前後の突合</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>S-09 S-11</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>2026-05の EMP-001（概算320,000・ヘルプ34,000・深夜9,000）／EMP-005（350,000・58,000・18,000）／EMP-003（144,000・13,000・0）を検算</t>
+          <t>移行を実施し、移行後の従業員一覧・設定履歴・直近3か月の人件費実績を出力して data/15 で突合</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
+          <t>件数の増減＝0／全項目の差分＝0／適用日付が空の行＝0／3か月とも人件費の差分＝0円</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr"/>
@@ -3296,49 +3296,49 @@
       <c r="K57" s="8" t="inlineStr"/>
       <c r="L57" s="8" t="inlineStr">
         <is>
-          <t>店舗別に振り替えても全社合計1,461,312円は不変（C-005で確認）</t>
+          <t>★No-Go条件。1件・1円でも動けばリリース中止</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>横断</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>S-03 S-04</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
+          <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr"/>
@@ -3346,49 +3346,49 @@
       <c r="K58" s="8" t="inlineStr"/>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>★No-Go条件。振替後の店舗別 S01=641,265／S02=141,616／S03=332,004／S04=311,250／S05=35,177 → 合計1,461,312円＝全社と一致</t>
+          <t>欠落0であること</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>横断</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>T-Z05</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>遷移と表示規則の網羅</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>S-07 ／ data/14を投入</t>
+          <t>S-04 S-05</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr"/>
@@ -3396,7 +3396,7 @@
       <c r="K59" s="8" t="inlineStr"/>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>暦日割で実装されていると333,333円になる（差606円）。この差でどちらの基準で実装されたか判別できる</t>
+          <t>キャンセル・戻るを含む</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -3418,27 +3418,27 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>S-07 ／ data/14を投入</t>
+          <t>S-03 S-07</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+          <t>2026-05の EMP-002（概算280,000・深夜2h=2,800）と EMP-007（概算300,000・深夜4h=6,000）を検算</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr"/>
@@ -3446,7 +3446,7 @@
       <c r="K60" s="8" t="inlineStr"/>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>時給者は日割り按分ではなく各勤務日の有効単価で計算されること</t>
+          <t>現行サンプルはこの2行のみ一致している</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -3468,27 +3468,27 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>T-S03実施済み S-07</t>
+          <t>S-03 S-07</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>2026-05を締めた状態で EMP-001に2026-05-10適用の改定を保存し、勤怠も再取込する（締め解除後の再計算は T-S05 で確認する）</t>
+          <t>2026-05の EMP-001（概算320,000・ヘルプ34,000・深夜9,000）／EMP-005（350,000・58,000・18,000）／EMP-003（144,000・13,000・0）を検算</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）</t>
+          <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
       <c r="K61" s="8" t="inlineStr"/>
       <c r="L61" s="8" t="inlineStr">
         <is>
-          <t>★No-Go条件。この機能の最重要リスク箇所。解除後の再計算は T-S05 の結果を使う（重複実施を避ける）</t>
+          <t>店舗別に振り替えても全社合計1,461,312円は不変（C-005で確認）</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -3518,27 +3518,27 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>S-03 S-04</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・10h）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
+          <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr"/>
@@ -3546,7 +3546,7 @@
       <c r="K62" s="8" t="inlineStr"/>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>再作成後は全行が算式どおり（EMP-001 深夜6h=18,000／EMP-002 2h=5,250／EMP-005 10h=32,812／EMP-007 4h=11,250）。みなし差分は5月は全員が未達のため超過支給0</t>
+          <t>★No-Go条件。振替後の店舗別 S01=641,265／S02=141,616／S03=332,004／S04=311,250／S05=35,177 → 合計1,461,312円＝全社と一致</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -3568,27 +3568,27 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>S-03 S-04</t>
+          <t>S-07 ／ data/14を投入</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+          <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -3596,207 +3596,207 @@
       <c r="K63" s="8" t="inlineStr"/>
       <c r="L63" s="8" t="inlineStr">
         <is>
-          <t>店舗別の交通費 S01=35,900／S02=9,700／S03=22,900／S04=30,000／S05=1,500（合計100,000円）</t>
+          <t>暦日割で実装されていると333,333円になる（差606円）。この差でどちらの基準で実装されたか判別できる</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="9" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>レビュー</t>
-        </is>
-      </c>
-      <c r="D64" s="10" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47</t>
-        </is>
-      </c>
-      <c r="E64" s="10" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="F64" s="10" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="G64" s="10" t="inlineStr">
-        <is>
-          <t>テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>①履歴テーブルへのUPDATE/DELETEが**0箇所**（INSERTのみ） ②従業員コードに一意制約が**1件**ある ③ヘルプ先交通費が「従業員×店舗」の**多対多**で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>C-011</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>AC-13</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>時給者の概算と月中改定</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>S-07 ／ data/14を投入</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr"/>
-      <c r="K64" s="10" t="inlineStr"/>
-      <c r="L64" s="10" t="inlineStr">
-        <is>
-          <t>★画面操作では判別できない。①が破られると過去が書き換わり得る（AC-03に連鎖）／③が単一値だと店舗ごとの実費が持てない</t>
+      <c r="K64" s="8" t="inlineStr"/>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>時給者は日割り按分ではなく各勤務日の有効単価で計算されること</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="9" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t>R-02</t>
-        </is>
-      </c>
-      <c r="C65" s="9" t="inlineStr">
-        <is>
-          <t>レビュー</t>
-        </is>
-      </c>
-      <c r="D65" s="10" t="inlineStr">
-        <is>
-          <t>AC-16 AC-41</t>
-        </is>
-      </c>
-      <c r="E65" s="10" t="inlineStr">
-        <is>
-          <t>締めの実装レビュー</t>
-        </is>
-      </c>
-      <c r="F65" s="10" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="G65" s="10" t="inlineStr">
-        <is>
-          <t>締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="inlineStr">
-        <is>
-          <t>①締め状態を保持する項目が**1つ**ある ②締め済み期間で再計算を行う経路が**0箇所**（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が**0箇所**</t>
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>C-008</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>AC-16</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>締めの前後で数字が動かないこと</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>T-S03実施済み S-07</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr">
+        <is>
+          <t>2026-05を締めた状態で EMP-001に2026-05-10適用の改定を保存し、勤怠も再取込する（締め解除後の再計算は T-S05 で確認する）</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="10" t="inlineStr">
-        <is>
-          <t>★画面では判別できない。③が画面側だけだと、APIを直接呼べば店長でも締められる</t>
+      <c r="K65" s="8" t="inlineStr"/>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>★No-Go条件。この機能の最重要リスク箇所。解除後の再計算は T-S05 の結果を使う（重複実施を避ける）</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="9" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>R-03</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>レビュー</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>AC-23 AC-42 AC-43</t>
-        </is>
-      </c>
-      <c r="E66" s="10" t="inlineStr">
-        <is>
-          <t>入力検証とトランザクションのレビュー</t>
-        </is>
-      </c>
-      <c r="F66" s="10" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="G66" s="10" t="inlineStr">
-        <is>
-          <t>取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>①必須項目のサーバ側チェックが**全項目**にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の**5種**をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が**1つ**に固定されている）</t>
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>C-013</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>AC-10 AC-14</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>S-03 S-07</t>
+        </is>
+      </c>
+      <c r="G66" s="8" t="inlineStr">
+        <is>
+          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・10h）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr"/>
-      <c r="K66" s="10" t="inlineStr"/>
-      <c r="L66" s="10" t="inlineStr">
-        <is>
-          <t>★T-R10・T-I05・T-I18は画面の挙動を見るもの。画面側だけの実装でも合格してしまうため、ここで裏を取る</t>
+      <c r="K66" s="8" t="inlineStr"/>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>再作成後は全行が算式どおり（EMP-001 深夜6h=18,000／EMP-002 2h=5,250／EMP-005 10h=32,812／EMP-007 4h=11,250）。みなし差分は5月は全員が未達のため超過支給0</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>R-04</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>レビュー</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>AC-35 AC-11</t>
-        </is>
-      </c>
-      <c r="E67" s="10" t="inlineStr">
-        <is>
-          <t>計算ロジックの共有レビュー</t>
-        </is>
-      </c>
-      <c r="F67" s="10" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
-        <is>
-          <t>人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>同じ集計ロジックを参照している（画面ごとの独自計算が**0箇所**）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も**1箇所**に集約されている</t>
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>AC-15</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>交通費の計上先</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>S-03 S-04</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr">
+        <is>
+          <t>EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr"/>
-      <c r="K67" s="10" t="inlineStr"/>
-      <c r="L67" s="10" t="inlineStr">
-        <is>
-          <t>★別計算だと、いま同じ数字でも改修のたびにずれる。AC-11（店舗別＝全社）が将来壊れる原因になる</t>
+      <c r="K67" s="8" t="inlineStr"/>
+      <c r="L67" s="8" t="inlineStr">
+        <is>
+          <t>店舗別の交通費 S01=35,900／S02=9,700／S03=22,900／S04=30,000／S05=1,500（合計100,000円）</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -3818,12 +3818,12 @@
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
       <c r="E68" s="10" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="F68" s="10" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>取込の列解決の実装を提示してもらう</t>
+          <t>テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
         </is>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
-          <t>CSVの列名がコードに直接書かれている箇所が**0箇所**。列の対応はマッピング設定から解決している</t>
+          <t>①履歴テーブルへのUPDATE/DELETEが**0箇所**（INSERTのみ） ②従業員コードに一意制約が**1件**ある ③ヘルプ先交通費が「従業員×店舗」の**多対多**で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr"/>
@@ -3846,17 +3846,267 @@
       <c r="K68" s="10" t="inlineStr"/>
       <c r="L68" s="10" t="inlineStr">
         <is>
+          <t>★画面操作では判別できない。①が破られると過去が書き換わり得る（AC-03に連鎖）／③が単一値だと店舗ごとの実費が持てない</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>R-02</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>レビュー</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>AC-16 AC-41</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>締めの実装レビュー</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>①締め状態を保持する項目が**1つ**ある ②締め済み期間で再計算を行う経路が**0箇所**（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が**0箇所**</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr"/>
+      <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="10" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>★画面では判別できない。③が画面側だけだと、APIを直接呼べば店長でも締められる</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>R-03</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>レビュー</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>AC-23 AC-42 AC-43</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>入力検証とトランザクションのレビュー</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>①必須項目のサーバ側チェックが**全項目**にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の**5種**をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が**1つ**に固定されている）</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr"/>
+      <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="10" t="inlineStr"/>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>★T-R10・T-I05・T-I18は画面の挙動を見るもの。画面側だけの実装でも合格してしまうため、ここで裏を取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>R-04</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>レビュー</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>AC-35 AC-11</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>計算ロジックの共有レビュー</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>同じ集計ロジックを参照している（画面ごとの独自計算が**0箇所**）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も**1箇所**に集約されている</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr"/>
+      <c r="J71" s="6" t="inlineStr"/>
+      <c r="K71" s="10" t="inlineStr"/>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>★別計算だと、いま同じ数字でも改修のたびにずれる。AC-11（店舗別＝全社）が将来壊れる原因になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>R-05</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>レビュー</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>AC-22 AC-24</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>列マッピングの実装レビュー</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>取込の列解決の実装を提示してもらう</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>CSVの列名がコードに直接書かれている箇所が**0箇所**。列の対応はマッピング設定から解決している</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr"/>
+      <c r="J72" s="6" t="inlineStr"/>
+      <c r="K72" s="10" t="inlineStr"/>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
           <t>★T-I04が合格しても、ジョブカンの列名をコードに埋め込んだ実装だと次の勤怠システムで開発が必要になる（K4・R5に直結）</t>
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C73" s="9" t="inlineStr">
+        <is>
+          <t>レビュー</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>設定更新の処理が**1箇所**に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr"/>
+      <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="10" t="inlineStr"/>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>★T-A09は画面の挙動を見るもの。別処理でたまたま両方に履歴が残る実装だと、改修時に片方が欠ける</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:L68"/>
+  <autoFilter ref="A3:L73"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <conditionalFormatting sqref="J4:J68">
+  <conditionalFormatting sqref="J4:J73">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"合格"</formula>
     </cfRule>
@@ -3865,7 +4115,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J4:J68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4:J73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未実装"</formula1>
     </dataValidation>
   </dataValidations>

--- a/20260804_従業員管理_02_検証プラン.xlsx
+++ b/20260804_従業員管理_02_検証プラン.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="検証プラン" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$3:$L$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'検証プラン'!$A$3:$L$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>従業員管理 検証プラン ─ 操作した結果が受入条件を満たすか（準備11行＋検証59件）</t>
+          <t>従業員管理 検証プラン ─ 操作した結果が受入条件を満たすか（準備11行＋検証60件）</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>data/07（KOT）・08（ジョブカン）・09（異常系）・10（給与設定）・11（先頭説明行あり）を手元に用意し、data/12（設定未入力のEMP-015）を投入。あわせて data/16・17（前回取込の差分確認用）を用意</t>
+          <t>data/07（KOT）・08（ジョブカン）・09（異常系）・10（給与設定）・11（先頭説明行あり）を手元に用意し、data/12（設定未入力のEMP-015）を投入。あわせて data/16・17（前回取込の差分確認用）を用意。data/18（列マッピング表のテンプレ）も用意</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -896,7 +896,7 @@
       <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>09は4行が別種のエラー（コード欠落／給与額-50,000／店舗S99／給与額abc・雇用区分「契約社員」） ／ 16・17は T-N02（前回差分表示）で使用</t>
+          <t>09は4行が別種のエラー（コード欠落／給与額-50,000／店舗S99／給与額abc・雇用区分「契約社員」） ／ 16・17は T-N02（前回差分表示）で使用 ／ 18は T-I19（マッピング表の一括登録）で使用</t>
         </is>
       </c>
     </row>
@@ -2333,12 +2333,12 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>年月＝2026-05を選び「締め」→ 確認モーダルの内容を確認 → 実行</t>
+          <t>年月＝2026-05を選び「2026-05 締め」→ 確認モーダル「月別実績締め処理の確認」の内容を確認 → 「締めを実行」</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>「締め後はデータの編集ができなくなります」の確認モーダルが**1回**出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
+          <t>「締めます。締め後はデータの編集ができなくなります。よろしいですか？」の確認が1回出る。実行でボタンが「2026-05 締め」→「2026-05 締め解除」に変わる（表記の切替=1箇所）</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -2483,12 +2483,12 @@
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
-          <t>「締め解除」→ 確認モーダル → 実行</t>
+          <t>「2026-05 締め解除」→ 確認モーダル「月別実績締め解除の確認」→「締め解除を実行」</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>「解除後はデータの編集が可能になります」の確認が出る（1回）。実行で編集可に戻り、C-008で保留されていた5/10からの改定が反映される。EMP-001の2026-05の実績給与＝**352,286円**（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）。締め前の338,000から+14,286円</t>
+          <t>「締めを解除します。解除後はデータの編集が可能になります。よろしいですか？」の確認が1回出る。実行で編集可に戻り、C-008で保留されていた5/10からの改定が反映されて再計算される。EMP-001の2026-05の実績給与＝352,286円（概算334,286＝320,000×6/21＋340,000×15/21、＋深夜18,000）</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
       <c r="K41" s="8" t="inlineStr"/>
       <c r="L41" s="8" t="inlineStr">
         <is>
-          <t>所定労働日割（判断1）で再計算される。暦日割で実装されていると概算333,548→実績351,548になり、この差738円で基準を判別できる</t>
+          <t>所定労働日割（判断1）で再計算される。暦日割なら351,548円で、差738円により基準を判別できる</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>従業員設定＝**6列**（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝**9列**（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
+          <t>従業員設定＝6列（従業員コード/氏名/雇用区分/所属店舗/ヘルプ先店舗/適用日付）、給与設定＝9列（従業員コード/給与単位/単位給与額/交通費単位/単位交通費/ヘルプ先交通費/所定労働時間/みなし残業時間/適用日付）。文字化け0箇所</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr"/>
@@ -2933,12 +2933,12 @@
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>「列マッピングテンプレート管理」→ 登録 → データ種類で絞り込み → 編集・削除 → 列マッピング表インポート → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択</t>
+          <t>「列マッピングテンプレート管理」→ テンプレート登録（行を追加して保存）→ データ種類で絞り込み → 編集（更新する）・削除 → ツールバー「設定インポートへ」→ インポート画面でテンプレートを選択 →「全解除」を押す</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>テンプレートが保存・絞り込み・編集・削除できる。マッピング表の一括登録ができる。往復導線が通る。選択すると取込列設定が自動で埋まる（手入力0項目）</t>
+          <t>テンプレートが保存・絞り込み・編集・削除できる。往復導線が通る（2経路とも到達）。テンプレート選択で取込列設定が自動で埋まる（手入力0項目）。「全解除」で取込チェックが一括で外れる</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr"/>
@@ -2946,19 +2946,19 @@
       <c r="K50" s="8" t="inlineStr"/>
       <c r="L50" s="8" t="inlineStr">
         <is>
-          <t>CSだけで完結できること（開発不要）が要件</t>
+          <t>CSだけで完結できること（開発なしで新しい勤怠システムに対応できる）が要件</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>出力</t>
+          <t>取込</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>T-E04</t>
+          <t>T-I19</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -2968,27 +2968,27 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>AC-25 AC-26 AC-30</t>
+          <t>AC-51</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>設定のエクスポート</t>
+          <t>マッピング表の一括登録</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-06</t>
         </is>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②対象＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
+          <t>列マッピングテンプレートで「テンプレートダウンロード」→ data/18 のように記入 →「マッピングテンプレートファイル」からアップロード → インポート。あわせて10MBを超えるファイルも試す</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
+          <t>テンプレートCSVがDLされ（文字化け0箇所）、アップロードでマッピングが一括反映される（10行なら10行）。10MB超は拒否される</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       <c r="K51" s="8" t="inlineStr"/>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>チェックしていない列が混入しないこと（情報の出し過ぎ防止）</t>
+          <t>行数が多い顧客はこの一括登録を使う。次段階の条件（AC-51）</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>T-E09</t>
+          <t>T-E04</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -3018,27 +3018,27 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>AC-25</t>
+          <t>AC-25 AC-26 AC-30</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>実績・同時のエクスポート</t>
+          <t>設定のエクスポート</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
+          <t>従業員一覧右上「設定・実績エクスポート」→ ①設定 → ②「対象（複数選択可）」＝従業員設定 → データ項目3つ（従業員コード・氏名・所属店舗）→ 出力。次に対象＝従業員設定＋給与設定 で出力</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
+          <t>専用画面が開き①②の2段構成。出力CSVは3列12行（過不足なし）。両対象を選ぶと2ファイル出力</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr"/>
@@ -3046,7 +3046,7 @@
       <c r="K52" s="8" t="inlineStr"/>
       <c r="L52" s="8" t="inlineStr">
         <is>
-          <t>①の複数選択が出力まで反映されること</t>
+          <t>チェックしていない列が混入しないこと（情報の出し過ぎ防止）</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>T-E07</t>
+          <t>T-E09</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -3068,27 +3068,27 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>AC-27 AC-28</t>
+          <t>AC-25</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>未選択の防止と文字化け</t>
+          <t>実績・同時のエクスポート</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>S-04</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>種別／対象／項目のいずれかを未選択のまま「エクスポート」→ その後T-E04の出力ファイルをExcelで開く</t>
+          <t>①実績 → ②月＝2026-05 → 実績のデータ項目（交通費・総支給額を含む9項目）→ 出力。次に ①設定＋実績 を両方選んで出力</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>警告が出て出力されない（空ファイルが落ちてこない）。日本語が文字化けしない（BOM付きUTF-8）</t>
+          <t>実績1ファイルが出力される。両方選択時は設定と実績の両方が出力される</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
@@ -3096,19 +3096,19 @@
       <c r="K53" s="8" t="inlineStr"/>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>そのまま外部提出できるかの判断</t>
+          <t>①の複数選択が出力まで反映されること</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>取込データ</t>
+          <t>出力</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>T-N01</t>
+          <t>T-E07</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -3118,27 +3118,27 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>AC-39</t>
+          <t>AC-27 AC-28</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>取込元データの確認</t>
+          <t>未選択の防止と文字化け</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>T-I03実施済み</t>
+          <t>S-04</t>
         </is>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
-          <t>サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
+          <t>種別／対象／項目のいずれかを未選択のまま「エクスポート」→ その後T-E04の出力ファイルをExcelで開く</t>
         </is>
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
+          <t>警告が出て出力されない（空ファイルが落ちてこない）。日本語が文字化けしない（BOM付きUTF-8）</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr"/>
@@ -3146,7 +3146,7 @@
       <c r="K54" s="8" t="inlineStr"/>
       <c r="L54" s="8" t="inlineStr">
         <is>
-          <t>履歴の「変更ソース＝CSVインポート」から辿れること</t>
+          <t>そのまま外部提出できるかの判断</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>T-N02</t>
+          <t>T-N01</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -3168,27 +3168,27 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>AC-50</t>
+          <t>AC-39</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>取込前のプレビューと前回差分</t>
+          <t>取込元データの確認</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>S-06 S-12</t>
+          <t>T-I03実施済み</t>
         </is>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す</t>
+          <t>サイドバー「設定取込データ」→ 取り込んだファイル・行を確認。次に「実績取込データ」を開く</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回330,000円→新規350,000円」の形式で差だけが表示される。読み込み＝取込中モーダルが出て完了する</t>
+          <t>設定取込データ＝取込データ名の一覧→タブ（従業員設定11列／給与設定4列）。実績取込データ＝一覧→タブ（月別データ12列／日別データ12列。いずれも交通費・総支給額を含む）</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr"/>
@@ -3196,7 +3196,7 @@
       <c r="K55" s="8" t="inlineStr"/>
       <c r="L55" s="8" t="inlineStr">
         <is>
-          <t>タブ（設定＝従業員設定/給与設定、実績＝月別データ/日別データ）も切り替わること</t>
+          <t>履歴の「変更ソース＝CSVインポート」から辿れること</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>T-N03</t>
+          <t>T-N02</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
@@ -3218,27 +3218,27 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>AC-30</t>
+          <t>AC-50</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>取込データと人件費実績の相互導線</t>
+          <t>取込前のプレビューと前回差分</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>S-05</t>
+          <t>S-06 S-12</t>
         </is>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
+          <t>設定取込データと実績取込データで、各行の「プレビュー」→「前回差分表示」→「読み込み」を順に押す</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>2経路とも到達する（不通=0）</t>
+          <t>プレビュー＝取込内容が一覧表示（設定11項目／実績は総労働時間・給与・交通費 ほか）。前回差分＝「前回330,000円→新規350,000円」の形式で差だけが表示される。読み込み＝取込中モーダルが出て完了する</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr"/>
@@ -3246,19 +3246,19 @@
       <c r="K56" s="8" t="inlineStr"/>
       <c r="L56" s="8" t="inlineStr">
         <is>
-          <t>行きと戻りの両方が通ること</t>
+          <t>タブ（設定＝従業員設定/給与設定、実績＝月別データ/日別データ）も切り替わること</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>横断</t>
+          <t>取込データ</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>T-Z01</t>
+          <t>T-N03</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -3268,27 +3268,27 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>AC-01 AC-02 AC-03</t>
+          <t>AC-30</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>移行前後の突合</t>
+          <t>取込データと人件費実績の相互導線</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>S-09 S-11</t>
+          <t>S-05</t>
         </is>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
-          <t>移行を実施し、移行後の従業員一覧・設定履歴・直近3か月の人件費実績を出力して data/15 で突合</t>
+          <t>人件費実績の「実績取込データへ」→ 実績取込データの「人件費実績へ」を押す</t>
         </is>
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>件数の増減＝0／全項目の差分＝0／適用日付が空の行＝0／3か月とも人件費の差分＝0円</t>
+          <t>2経路とも到達する（不通=0）</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr"/>
@@ -3296,7 +3296,7 @@
       <c r="K57" s="8" t="inlineStr"/>
       <c r="L57" s="8" t="inlineStr">
         <is>
-          <t>★No-Go条件。1件・1円でも動けばリリース中止</t>
+          <t>行きと戻りの両方が通ること</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>T-Z04</t>
+          <t>T-Z01</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -3318,27 +3318,27 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>AC-29</t>
+          <t>AC-01 AC-02 AC-03</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>サイドバーの構成</t>
+          <t>移行前後の突合</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>S-01</t>
+          <t>S-09 S-11</t>
         </is>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
-          <t>PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
+          <t>移行を実施し、移行後の従業員一覧・設定履歴・直近3か月の人件費実績を出力して data/15 で突合</t>
         </is>
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
+          <t>件数の増減＝0／全項目の差分＝0／適用日付が空の行＝0／3か月とも人件費の差分＝0円</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr"/>
@@ -3346,7 +3346,7 @@
       <c r="K58" s="8" t="inlineStr"/>
       <c r="L58" s="8" t="inlineStr">
         <is>
-          <t>欠落0であること</t>
+          <t>★No-Go条件。1件・1円でも動けばリリース中止</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>T-Z05</t>
+          <t>T-Z04</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -3368,27 +3368,27 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>AC-30 AC-01</t>
+          <t>AC-29</t>
         </is>
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>遷移と表示規則の網羅</t>
+          <t>サイドバーの構成</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>S-04 S-05</t>
+          <t>S-01</t>
         </is>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
+          <t>PC（ホバー展開）とモバイル（アコーディオン）で「従業員管理」を開く</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
+          <t>閲覧・管理3項目／データ連携4項目の計7項目が両端末で表示</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr"/>
@@ -3396,49 +3396,49 @@
       <c r="K59" s="8" t="inlineStr"/>
       <c r="L59" s="8" t="inlineStr">
         <is>
-          <t>キャンセル・戻るを含む</t>
+          <t>欠落0であること</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>横断</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>C-001</t>
+          <t>T-Z05</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>計算</t>
+          <t>操作</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>AC-10</t>
+          <t>AC-30 AC-01</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプなし）</t>
+          <t>遷移と表示規則の網羅</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>S-04 S-05</t>
         </is>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>2026-05の EMP-002（概算280,000・深夜2h=2,800）と EMP-007（概算300,000・深夜4h=6,000）を検算</t>
+          <t>仕様書 第2部のケース別遷移フロー（分岐込み75本）を順に押下し、各画面の通貨・バッジ・空表示を確認</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
+          <t>すべて到達可能（不通＝0）。通貨は千区切り＋¥、バッジ規則が全画面で同一、空データは「データはありません。」</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr"/>
@@ -3446,7 +3446,7 @@
       <c r="K60" s="8" t="inlineStr"/>
       <c r="L60" s="8" t="inlineStr">
         <is>
-          <t>現行サンプルはこの2行のみ一致している</t>
+          <t>キャンセル・戻るを含む</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>C-003</t>
+          <t>C-001</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-10</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>実績給与の内訳整合（ヘルプあり）</t>
+          <t>実績給与の内訳整合（ヘルプなし）</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>2026-05の EMP-001（概算320,000・ヘルプ34,000・深夜9,000）／EMP-005（350,000・58,000・18,000）／EMP-003（144,000・13,000・0）を検算</t>
+          <t>2026-05の EMP-002（概算280,000・深夜2h=2,800）と EMP-007（概算300,000・深夜4h=6,000）を検算</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
+          <t>EMP-002＝282,800／EMP-007＝306,000（差分0円）</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr"/>
@@ -3496,7 +3496,7 @@
       <c r="K61" s="8" t="inlineStr"/>
       <c r="L61" s="8" t="inlineStr">
         <is>
-          <t>店舗別に振り替えても全社合計1,461,312円は不変（C-005で確認）</t>
+          <t>現行サンプルはこの2行のみ一致している</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>C-005</t>
+          <t>C-003</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -3518,27 +3518,27 @@
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>AC-11</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>店舗別合計と全社合計の一致</t>
+          <t>実績給与の内訳整合（ヘルプあり）</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>S-03 S-04</t>
+          <t>S-03 S-07</t>
         </is>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
+          <t>2026-05の EMP-001（概算320,000・ヘルプ34,000・深夜9,000）／EMP-005（350,000・58,000・18,000）／EMP-003（144,000・13,000・0）を検算</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
+          <t>EMP-001＝338,000（概算320,000＋深夜18,000）／EMP-005＝382,812（350,000＋32,812）／EMP-003＝144,000。ヘルプ人件費は実績給与を労働時間で按分し応援先へ振替（EMP-001=43,232／EMP-003=24,000／EMP-005=72,424）</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr"/>
@@ -3546,7 +3546,7 @@
       <c r="K62" s="8" t="inlineStr"/>
       <c r="L62" s="8" t="inlineStr">
         <is>
-          <t>★No-Go条件。振替後の店舗別 S01=641,265／S02=141,616／S03=332,004／S04=311,250／S05=35,177 → 合計1,461,312円＝全社と一致</t>
+          <t>店舗別に振り替えても全社合計1,461,312円は不変（C-005で確認）</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>C-006</t>
+          <t>C-005</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -3568,27 +3568,27 @@
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>AC-12 AC-04</t>
+          <t>AC-11</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>月中改定と予約の日割り</t>
+          <t>店舗別合計と全社合計の一致</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>S-07 ／ data/14を投入</t>
+          <t>S-03 S-04</t>
         </is>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
-          <t>EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
+          <t>2026-05・実績モードで店舗フィルタを5店それぞれに設定して合計し、全社と突合</t>
         </is>
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
+          <t>店舗5店の合計 − 全社合計 ＝ 0円（1,461,312円）</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -3596,7 +3596,7 @@
       <c r="K63" s="8" t="inlineStr"/>
       <c r="L63" s="8" t="inlineStr">
         <is>
-          <t>暦日割で実装されていると333,333円になる（差606円）。この差でどちらの基準で実装されたか判別できる</t>
+          <t>★No-Go条件。振替後の店舗別 S01=641,265／S02=141,616／S03=332,004／S04=311,250／S05=35,177 → 合計1,461,312円＝全社と一致</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>C-011</t>
+          <t>C-006</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>AC-13</t>
+          <t>AC-12 AC-04</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>時給者の概算と月中改定</t>
+          <t>月中改定と予約の日割り</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
-          <t>EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
+          <t>EMP-001を2026-06-11から340,000に改定（6月の勤務は22日176h）。次に2026-08-01適用で予約し7月・8月を確認</t>
         </is>
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
+          <t>6月＝332,727円（320,000×8/22 ＋ 340,000×14/22。判断1＝所定労働日割）。7月＝320,000満額・8月＝340,000満額（月初適用のため日割りなし）</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
       <c r="K64" s="8" t="inlineStr"/>
       <c r="L64" s="8" t="inlineStr">
         <is>
-          <t>時給者は日割り按分ではなく各勤務日の有効単価で計算されること</t>
+          <t>暦日割で実装されていると333,333円になる（差606円）。この差でどちらの基準で実装されたか判別できる</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>C-008</t>
+          <t>C-011</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -3668,27 +3668,27 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>AC-16</t>
+          <t>AC-13</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>締めの前後で数字が動かないこと</t>
+          <t>時給者の概算と月中改定</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>T-S03実施済み S-07</t>
+          <t>S-07 ／ data/14を投入</t>
         </is>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
-          <t>2026-05を締めた状態で EMP-001に2026-05-10適用の改定を保存し、勤怠も再取込する（締め解除後の再計算は T-S05 で確認する）</t>
+          <t>EMP-003の2026-05の概算（時給1,200×所定120h）と、2026-06-16から1,250へ改定した6月（前半60h・後半60h）を検算</t>
         </is>
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）</t>
+          <t>5月＝144,000／6月＝1,200×60＋1,250×60＝147,000</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr"/>
@@ -3696,7 +3696,7 @@
       <c r="K65" s="8" t="inlineStr"/>
       <c r="L65" s="8" t="inlineStr">
         <is>
-          <t>★No-Go条件。この機能の最重要リスク箇所。解除後の再計算は T-S05 の結果を使う（重複実施を避ける）</t>
+          <t>時給者は日割り按分ではなく各勤務日の有効単価で計算されること</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>C-013</t>
+          <t>C-008</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr">
@@ -3718,27 +3718,27 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>AC-10 AC-14</t>
+          <t>AC-16</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
+          <t>締めの前後で数字が動かないこと</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>S-03 S-07</t>
+          <t>T-S03実施済み S-07</t>
         </is>
       </c>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・10h）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
+          <t>2026-05を締めた状態で EMP-001に2026-05-10適用の改定を保存し、勤怠も再取込する（締め解除後の再計算は T-S05 で確認する）</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
+          <t>5月の実績給与・総労働時間の差分＝0円（338,000のまま動かない）</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
       <c r="K66" s="8" t="inlineStr"/>
       <c r="L66" s="8" t="inlineStr">
         <is>
-          <t>再作成後は全行が算式どおり（EMP-001 深夜6h=18,000／EMP-002 2h=5,250／EMP-005 10h=32,812／EMP-007 4h=11,250）。みなし差分は5月は全員が未達のため超過支給0</t>
+          <t>★No-Go条件。この機能の最重要リスク箇所。解除後の再計算は T-S05 の結果を使う（重複実施を避ける）</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3758,7 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>C-017</t>
+          <t>C-013</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
@@ -3768,27 +3768,27 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>AC-15</t>
+          <t>AC-10 AC-14</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>交通費の計上先</t>
+          <t>単価の算式（深夜残業代・ヘルプ人件費・みなし差分）</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>S-03 S-04</t>
+          <t>S-03 S-07</t>
         </is>
       </c>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+          <t>深夜残業代÷深夜残業時間 と基礎時給の倍率、EMP-001の5/8（S02・10h）のヘルプ人件費、総労働−（所定＋みなし）を検算</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
+          <t>判断7（暫定）＝基礎時給×1.5。ヘルプ人件費＝当日の有効単価×ヘルプ時間（2,000×10＝20,000）。計上先はS02</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr"/>
@@ -3796,57 +3796,57 @@
       <c r="K67" s="8" t="inlineStr"/>
       <c r="L67" s="8" t="inlineStr">
         <is>
-          <t>店舗別の交通費 S01=35,900／S02=9,700／S03=22,900／S04=30,000／S05=1,500（合計100,000円）</t>
+          <t>再作成後は全行が算式どおり（EMP-001 深夜6h=18,000／EMP-002 2h=5,250／EMP-005 10h=32,812／EMP-007 4h=11,250）。みなし差分は5月は全員が未達のため超過支給0</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>実装レビュー</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>R-01</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>レビュー</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>AC-07 AC-40 AC-47</t>
-        </is>
-      </c>
-      <c r="E68" s="10" t="inlineStr">
-        <is>
-          <t>データ構造のレビュー</t>
-        </is>
-      </c>
-      <c r="F68" s="10" t="inlineStr">
-        <is>
-          <t>S-01</t>
-        </is>
-      </c>
-      <c r="G68" s="10" t="inlineStr">
-        <is>
-          <t>テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>①履歴テーブルへのUPDATE/DELETEが**0箇所**（INSERTのみ） ②従業員コードに一意制約が**1件**ある ③ヘルプ先交通費が「従業員×店舗」の**多対多**で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>C-017</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>計算</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>AC-15</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>交通費の計上先</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
+        <is>
+          <t>S-03 S-04</t>
+        </is>
+      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>EMP-001（単位交通費 月額18,000／ヘルプ先交通費 S02=700・S03=900）で2026-05の実績の全列と、5/8のS02勤務日を確認</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>交通費は実績給与に含まれない（独立費目）。通勤18,000は所属店舗S01、ヘルプ先交通費1,600（S02=700・S03=900）は各応援先に計上。人件費実績の「交通費」「総支給額」列で確認</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr"/>
       <c r="J68" s="6" t="inlineStr"/>
-      <c r="K68" s="10" t="inlineStr"/>
-      <c r="L68" s="10" t="inlineStr">
-        <is>
-          <t>★画面操作では判別できない。①が破られると過去が書き換わり得る（AC-03に連鎖）／③が単一値だと店舗ごとの実費が持てない</t>
+      <c r="K68" s="8" t="inlineStr"/>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>店舗別の交通費 S01=35,900／S02=9,700／S03=22,900／S04=30,000／S05=1,500（合計100,000円）</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>R-02</t>
+          <t>R-01</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>AC-16 AC-41</t>
+          <t>AC-07 AC-40 AC-47</t>
         </is>
       </c>
       <c r="E69" s="10" t="inlineStr">
         <is>
-          <t>締めの実装レビュー</t>
+          <t>データ構造のレビュー</t>
         </is>
       </c>
       <c r="F69" s="10" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
+          <t>テーブル定義（スキーマ）を提示してもらい、①設定履歴のUPDATE/DELETE ②従業員コードの制約 ③ヘルプ先交通費の持ち方 を確認する</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>①締め状態を保持する項目が**1つ**ある ②締め済み期間で再計算を行う経路が**0箇所**（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が**0箇所**</t>
+          <t>①履歴テーブルへのUPDATE/DELETEが**0箇所**（INSERTのみ） ②従業員コードに一意制約が**1件**ある ③ヘルプ先交通費が「従業員×店舗」の**多対多**で保持されている（従業員に1つの値だけを持つ実装ではない）</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr"/>
@@ -3896,7 +3896,7 @@
       <c r="K69" s="10" t="inlineStr"/>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>★画面では判別できない。③が画面側だけだと、APIを直接呼べば店長でも締められる</t>
+          <t>★画面操作では判別できない。①が破られると過去が書き換わり得る（AC-03に連鎖）／③が単一値だと店舗ごとの実費が持てない</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>R-03</t>
+          <t>R-02</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>AC-23 AC-42 AC-43</t>
+          <t>AC-16 AC-41</t>
         </is>
       </c>
       <c r="E70" s="10" t="inlineStr">
         <is>
-          <t>入力検証とトランザクションのレビュー</t>
+          <t>締めの実装レビュー</t>
         </is>
       </c>
       <c r="F70" s="10" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
+          <t>締めの実装を提示してもらい、①締め状態の保持 ②締め済み期間の再計算 ③締めAPIの権限 を確認する</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
-          <t>①必須項目のサーバ側チェックが**全項目**にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の**5種**をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が**1つ**に固定されている）</t>
+          <t>①締め状態を保持する項目が**1つ**ある ②締め済み期間で再計算を行う経路が**0箇所**（設定変更・勤怠取込の両方） ③締めAPIが会社スコープ権限で制限され、画面側だけの制御が**0箇所**</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr"/>
@@ -3946,7 +3946,7 @@
       <c r="K70" s="10" t="inlineStr"/>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>★T-R10・T-I05・T-I18は画面の挙動を見るもの。画面側だけの実装でも合格してしまうため、ここで裏を取る</t>
+          <t>★画面では判別できない。③が画面側だけだと、APIを直接呼べば店長でも締められる</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>R-04</t>
+          <t>R-03</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>AC-35 AC-11</t>
+          <t>AC-23 AC-42 AC-43</t>
         </is>
       </c>
       <c r="E71" s="10" t="inlineStr">
         <is>
-          <t>計算ロジックの共有レビュー</t>
+          <t>入力検証とトランザクションのレビュー</t>
         </is>
       </c>
       <c r="F71" s="10" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
+          <t>取込・登録の実装を提示してもらい、①必須チェック ②取込の検証 ③失敗時の巻き戻し を確認する</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>同じ集計ロジックを参照している（画面ごとの独自計算が**0箇所**）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も**1箇所**に集約されている</t>
+          <t>①必須項目のサーバ側チェックが**全項目**にある（画面側だけが0箇所） ②コード欠落/負値/未登録店舗/型不正/未定義区分の**5種**をサーバ側で検証 ③取込失敗時に部分登録が残らない（トランザクション、または行単位で結果を明示する実装が**1つ**に固定されている）</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr"/>
@@ -3996,7 +3996,7 @@
       <c r="K71" s="10" t="inlineStr"/>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>★別計算だと、いま同じ数字でも改修のたびにずれる。AC-11（店舗別＝全社）が将来壊れる原因になる</t>
+          <t>★T-R10・T-I05・T-I18は画面の挙動を見るもの。画面側だけの実装でも合格してしまうため、ここで裏を取る</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>R-05</t>
+          <t>R-04</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -4018,12 +4018,12 @@
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>AC-22 AC-24</t>
+          <t>AC-35 AC-11</t>
         </is>
       </c>
       <c r="E72" s="10" t="inlineStr">
         <is>
-          <t>列マッピングの実装レビュー</t>
+          <t>計算ロジックの共有レビュー</t>
         </is>
       </c>
       <c r="F72" s="10" t="inlineStr">
@@ -4033,12 +4033,12 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>取込の列解決の実装を提示してもらう</t>
+          <t>人件費実績・従業員詳細・エクスポートの3経路で、金額を計算している箇所を提示してもらう</t>
         </is>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>CSVの列名がコードに直接書かれている箇所が**0箇所**。列の対応はマッピング設定から解決している</t>
+          <t>同じ集計ロジックを参照している（画面ごとの独自計算が**0箇所**）。ヘルプ人件費の按分と端数処理（所属店舗へ寄せる）も**1箇所**に集約されている</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr"/>
@@ -4046,7 +4046,7 @@
       <c r="K72" s="10" t="inlineStr"/>
       <c r="L72" s="10" t="inlineStr">
         <is>
-          <t>★T-I04が合格しても、ジョブカンの列名をコードに埋め込んだ実装だと次の勤怠システムで開発が必要になる（K4・R5に直結）</t>
+          <t>★別計算だと、いま同じ数字でも改修のたびにずれる。AC-11（店舗別＝全社）が将来壊れる原因になる</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>R-06</t>
+          <t>R-05</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>AC-49</t>
+          <t>AC-22 AC-24</t>
         </is>
       </c>
       <c r="E73" s="10" t="inlineStr">
         <is>
-          <t>設定更新処理の共通化レビュー</t>
+          <t>列マッピングの実装レビュー</t>
         </is>
       </c>
       <c r="F73" s="10" t="inlineStr">
@@ -4083,12 +4083,12 @@
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+          <t>取込の列解決の実装を提示してもらう</t>
         </is>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>設定更新の処理が**1箇所**に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+          <t>CSVの列名がコードに直接書かれている箇所が**0箇所**。列の対応はマッピング設定から解決している</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr"/>
@@ -4096,17 +4096,67 @@
       <c r="K73" s="10" t="inlineStr"/>
       <c r="L73" s="10" t="inlineStr">
         <is>
+          <t>★T-I04が合格しても、ジョブカンの列名をコードに埋め込んだ実装だと次の勤怠システムで開発が必要になる（K4・R5に直結）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>実装レビュー</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>R-06</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>レビュー</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>AC-49</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>設定更新処理の共通化レビュー</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>S-01</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>従業員詳細とモーダルの2経路で、設定を更新している処理を提示してもらう</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>設定更新の処理が**1箇所**に集約され、両方の画面から同じ処理を呼んでいる（画面ごとの独自更新=0箇所）。履歴の記録も同じ処理内で行われる</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr"/>
+      <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="10" t="inlineStr"/>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
           <t>★T-A09は画面の挙動を見るもの。別処理でたまたま両方に履歴が残る実装だと、改修時に片方が欠ける</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L73"/>
+  <autoFilter ref="A3:L74"/>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A1:L1"/>
   </mergeCells>
-  <conditionalFormatting sqref="J4:J73">
+  <conditionalFormatting sqref="J4:J74">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"合格"</formula>
     </cfRule>
@@ -4115,7 +4165,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="J4:J73" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J4:J74" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"合格,不合格,未実装"</formula1>
     </dataValidation>
   </dataValidations>
